--- a/backups/Timesheet_2026-06-01.xlsx
+++ b/backups/Timesheet_2026-06-01.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="179">
   <si>
     <t>Month</t>
   </si>
@@ -41,6 +41,9 @@
     <t>FM - OTHER</t>
   </si>
   <si>
+    <t>APPs / Money Motive</t>
+  </si>
+  <si>
     <t>Total Done</t>
   </si>
   <si>
@@ -341,7 +344,7 @@
     <t>Protein - 40 G</t>
   </si>
   <si>
-    <t>Diet Control</t>
+    <t>1800 Calories</t>
   </si>
   <si>
     <t>Workout</t>
@@ -514,9 +517,21 @@
     <t>Puppy dog Toy</t>
   </si>
   <si>
+    <t>Playstation</t>
+  </si>
+  <si>
     <t>Fancy Towel</t>
   </si>
   <si>
+    <t>English Willow Bat</t>
+  </si>
+  <si>
+    <t>Cycle Pump</t>
+  </si>
+  <si>
+    <t>Cricket Shoes</t>
+  </si>
+  <si>
     <t>Home</t>
   </si>
   <si>
@@ -559,10 +574,16 @@
     <t>Family outing New Places</t>
   </si>
   <si>
-    <t>EATABLES</t>
-  </si>
-  <si>
-    <t>nON EATBALES</t>
+    <t>new EATABLES</t>
+  </si>
+  <si>
+    <t>new nON EATBALES</t>
+  </si>
+  <si>
+    <t>old eatbles</t>
+  </si>
+  <si>
+    <t>old non eatables</t>
   </si>
   <si>
     <t>Cheesy me - Near Chrompet railway station backside</t>
@@ -581,6 +602,9 @@
   </si>
   <si>
     <t xml:space="preserve">Hasthinapuram MIT Flyover Park </t>
+  </si>
+  <si>
+    <t>FB World</t>
   </si>
 </sst>
 </file>
@@ -1012,18 +1036,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
-    <col min="12" max="12" width="36" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1060,81 +1084,90 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2">
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
+      <c r="C3" s="2">
+        <v>3</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.5</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2.25</v>
       </c>
       <c r="I3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>13</v>
+        <v>5.75</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.35</v>
+      </c>
+      <c r="K3" s="2">
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1158,10 +1191,10 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -1179,1005 +1212,1005 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="J4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2188,23 +2221,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="3" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -2222,973 +2255,1066 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.25</v>
+      </c>
+      <c r="I2" s="2">
+        <v>5.75</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>13</v>
+        <v>64</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3209,142 +3335,142 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3364,172 +3490,172 @@
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3548,157 +3674,157 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +3835,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="35" customWidth="1"/>
@@ -3717,240 +3843,291 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
+      <c r="C13" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3961,63 +4138,99 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="35" customWidth="1"/>
+    <col min="1" max="4" width="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
